--- a/diseases/d103/2015-2019.xlsx
+++ b/diseases/d103/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6102,6 +6282,11 @@
       <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
